--- a/Documents/HBase/Moment冷热分离测试/Complete_STT.xlsx
+++ b/Documents/HBase/Moment冷热分离测试/Complete_STT.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Pet-Care-Ecosystem\Documents\HBase\Moment冷热分离测试\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56ACBCE9-0D70-470B-A068-5767438C2618}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FFFEE2A-5E3F-415F-9DD4-7F7C18036797}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="完整状态转移表" sheetId="1" r:id="rId1"/>
@@ -175,7 +175,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -191,6 +191,21 @@
     </font>
     <font>
       <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
@@ -232,11 +247,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -567,70 +584,70 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="C2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="A3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E3" t="s">
+      <c r="C3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="A4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="C4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="A5" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E5" t="s">
+      <c r="C5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>7</v>
       </c>
     </row>
@@ -652,121 +669,121 @@
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="A7" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C7" t="s">
-        <v>7</v>
-      </c>
-      <c r="D7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E7" t="s">
+      <c r="C7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+      <c r="A8" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E8" t="s">
+      <c r="C8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="A9" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C9" t="s">
-        <v>7</v>
-      </c>
-      <c r="D9" t="s">
-        <v>7</v>
-      </c>
-      <c r="E9" t="s">
+      <c r="C9" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="A10" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C10" t="s">
-        <v>7</v>
-      </c>
-      <c r="D10" t="s">
-        <v>7</v>
-      </c>
-      <c r="E10" t="s">
+      <c r="C10" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+      <c r="A11" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C11" t="s">
-        <v>7</v>
-      </c>
-      <c r="D11" t="s">
-        <v>7</v>
-      </c>
-      <c r="E11" t="s">
+      <c r="C11" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+      <c r="A12" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C12" t="s">
-        <v>7</v>
-      </c>
-      <c r="D12" t="s">
-        <v>7</v>
-      </c>
-      <c r="E12" t="s">
+      <c r="C12" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+      <c r="A13" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C13" t="s">
-        <v>7</v>
-      </c>
-      <c r="D13" t="s">
-        <v>7</v>
-      </c>
-      <c r="E13" t="s">
+      <c r="C13" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>7</v>
       </c>
     </row>
@@ -788,104 +805,104 @@
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+      <c r="A15" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C15" t="s">
-        <v>7</v>
-      </c>
-      <c r="D15" t="s">
-        <v>7</v>
-      </c>
-      <c r="E15" t="s">
+      <c r="C15" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+      <c r="A16" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C16" t="s">
-        <v>7</v>
-      </c>
-      <c r="D16" t="s">
-        <v>7</v>
-      </c>
-      <c r="E16" t="s">
+      <c r="C16" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+      <c r="A17" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C17" t="s">
-        <v>7</v>
-      </c>
-      <c r="D17" t="s">
-        <v>7</v>
-      </c>
-      <c r="E17" t="s">
+      <c r="C17" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+      <c r="A18" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C18" t="s">
-        <v>7</v>
-      </c>
-      <c r="D18" t="s">
-        <v>7</v>
-      </c>
-      <c r="E18" t="s">
+      <c r="C18" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+      <c r="A19" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C19" t="s">
-        <v>7</v>
-      </c>
-      <c r="D19" t="s">
-        <v>7</v>
-      </c>
-      <c r="E19" t="s">
+      <c r="C19" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+      <c r="A20" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C20" t="s">
-        <v>7</v>
-      </c>
-      <c r="D20" t="s">
-        <v>7</v>
-      </c>
-      <c r="E20" t="s">
+      <c r="C20" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>7</v>
       </c>
     </row>
@@ -907,36 +924,36 @@
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+      <c r="A22" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C22" t="s">
-        <v>7</v>
-      </c>
-      <c r="D22" t="s">
-        <v>7</v>
-      </c>
-      <c r="E22" t="s">
+      <c r="C22" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E22" s="3" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+      <c r="A23" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C23" t="s">
-        <v>7</v>
-      </c>
-      <c r="D23" t="s">
-        <v>7</v>
-      </c>
-      <c r="E23" t="s">
+      <c r="C23" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E23" s="3" t="s">
         <v>7</v>
       </c>
     </row>
@@ -958,104 +975,104 @@
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>27</v>
-      </c>
-      <c r="B25" t="s">
+      <c r="A25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B25" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C25" t="s">
-        <v>7</v>
-      </c>
-      <c r="D25" t="s">
-        <v>7</v>
-      </c>
-      <c r="E25" t="s">
+      <c r="C25" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>27</v>
-      </c>
-      <c r="B26" t="s">
+      <c r="A26" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B26" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C26" t="s">
-        <v>7</v>
-      </c>
-      <c r="D26" t="s">
-        <v>7</v>
-      </c>
-      <c r="E26" t="s">
+      <c r="C26" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E26" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>27</v>
-      </c>
-      <c r="B27" t="s">
+      <c r="A27" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B27" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C27" t="s">
-        <v>7</v>
-      </c>
-      <c r="D27" t="s">
-        <v>7</v>
-      </c>
-      <c r="E27" t="s">
+      <c r="C27" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>27</v>
-      </c>
-      <c r="B28" t="s">
+      <c r="A28" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B28" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C28" t="s">
-        <v>7</v>
-      </c>
-      <c r="D28" t="s">
-        <v>7</v>
-      </c>
-      <c r="E28" t="s">
+      <c r="C28" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E28" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>27</v>
-      </c>
-      <c r="B29" t="s">
+      <c r="A29" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B29" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C29" t="s">
-        <v>7</v>
-      </c>
-      <c r="D29" t="s">
-        <v>7</v>
-      </c>
-      <c r="E29" t="s">
+      <c r="C29" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E29" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>27</v>
-      </c>
-      <c r="B30" t="s">
+      <c r="A30" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B30" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C30" t="s">
-        <v>7</v>
-      </c>
-      <c r="D30" t="s">
-        <v>7</v>
-      </c>
-      <c r="E30" t="s">
+      <c r="C30" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E30" s="2" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1077,19 +1094,19 @@
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>27</v>
-      </c>
-      <c r="B32" t="s">
+      <c r="A32" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B32" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C32" t="s">
-        <v>7</v>
-      </c>
-      <c r="D32" t="s">
-        <v>7</v>
-      </c>
-      <c r="E32" t="s">
+      <c r="C32" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E32" s="3" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1128,36 +1145,36 @@
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
+      <c r="A35" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B35" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C35" t="s">
-        <v>7</v>
-      </c>
-      <c r="D35" t="s">
-        <v>7</v>
-      </c>
-      <c r="E35" t="s">
+      <c r="C35" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E35" s="3" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
+      <c r="A36" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B36" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C36" t="s">
-        <v>7</v>
-      </c>
-      <c r="D36" t="s">
-        <v>7</v>
-      </c>
-      <c r="E36" t="s">
+      <c r="C36" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E36" s="3" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1196,206 +1213,206 @@
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
+      <c r="A39" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B39" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C39" t="s">
-        <v>7</v>
-      </c>
-      <c r="D39" t="s">
-        <v>7</v>
-      </c>
-      <c r="E39" t="s">
+      <c r="C39" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E39" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
+      <c r="A40" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B40" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C40" t="s">
-        <v>7</v>
-      </c>
-      <c r="D40" t="s">
-        <v>7</v>
-      </c>
-      <c r="E40" t="s">
+      <c r="C40" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E40" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
+      <c r="A41" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B41" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C41" t="s">
-        <v>7</v>
-      </c>
-      <c r="D41" t="s">
-        <v>7</v>
-      </c>
-      <c r="E41" t="s">
+      <c r="C41" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E41" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
+      <c r="A42" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B42" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C42" t="s">
-        <v>7</v>
-      </c>
-      <c r="D42" t="s">
-        <v>7</v>
-      </c>
-      <c r="E42" t="s">
+      <c r="C42" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E42" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
+      <c r="A43" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B43" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C43" t="s">
-        <v>7</v>
-      </c>
-      <c r="D43" t="s">
-        <v>7</v>
-      </c>
-      <c r="E43" t="s">
+      <c r="C43" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E43" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
+      <c r="A44" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B44" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C44" t="s">
-        <v>7</v>
-      </c>
-      <c r="D44" t="s">
-        <v>7</v>
-      </c>
-      <c r="E44" t="s">
+      <c r="C44" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E44" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
+      <c r="A45" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B45" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C45" t="s">
-        <v>7</v>
-      </c>
-      <c r="D45" t="s">
-        <v>7</v>
-      </c>
-      <c r="E45" t="s">
+      <c r="C45" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E45" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
+      <c r="A46" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B46" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C46" t="s">
-        <v>7</v>
-      </c>
-      <c r="D46" t="s">
-        <v>7</v>
-      </c>
-      <c r="E46" t="s">
+      <c r="C46" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E46" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
+      <c r="A47" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B47" t="s">
+      <c r="B47" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C47" t="s">
-        <v>7</v>
-      </c>
-      <c r="D47" t="s">
-        <v>7</v>
-      </c>
-      <c r="E47" t="s">
+      <c r="C47" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E47" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
+      <c r="A48" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B48" t="s">
+      <c r="B48" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C48" t="s">
-        <v>7</v>
-      </c>
-      <c r="D48" t="s">
-        <v>7</v>
-      </c>
-      <c r="E48" t="s">
+      <c r="C48" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E48" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
+      <c r="A49" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B49" t="s">
+      <c r="B49" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C49" t="s">
-        <v>7</v>
-      </c>
-      <c r="D49" t="s">
-        <v>7</v>
-      </c>
-      <c r="E49" t="s">
+      <c r="C49" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E49" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
+      <c r="A50" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B50" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C50" t="s">
-        <v>7</v>
-      </c>
-      <c r="D50" t="s">
-        <v>7</v>
-      </c>
-      <c r="E50" t="s">
+      <c r="C50" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E50" s="2" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1434,104 +1451,104 @@
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
+      <c r="A53" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B53" t="s">
+      <c r="B53" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C53" t="s">
-        <v>7</v>
-      </c>
-      <c r="D53" t="s">
-        <v>7</v>
-      </c>
-      <c r="E53" t="s">
+      <c r="C53" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E53" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
+      <c r="A54" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B54" t="s">
+      <c r="B54" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C54" t="s">
-        <v>7</v>
-      </c>
-      <c r="D54" t="s">
-        <v>7</v>
-      </c>
-      <c r="E54" t="s">
+      <c r="C54" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E54" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
+      <c r="A55" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B55" t="s">
+      <c r="B55" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C55" t="s">
-        <v>7</v>
-      </c>
-      <c r="D55" t="s">
-        <v>7</v>
-      </c>
-      <c r="E55" t="s">
+      <c r="C55" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E55" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
+      <c r="A56" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B56" t="s">
+      <c r="B56" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C56" t="s">
-        <v>7</v>
-      </c>
-      <c r="D56" t="s">
-        <v>7</v>
-      </c>
-      <c r="E56" t="s">
+      <c r="C56" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E56" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
+      <c r="A57" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B57" t="s">
+      <c r="B57" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C57" t="s">
-        <v>7</v>
-      </c>
-      <c r="D57" t="s">
-        <v>7</v>
-      </c>
-      <c r="E57" t="s">
+      <c r="C57" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E57" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
+      <c r="A58" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B58" t="s">
+      <c r="B58" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C58" t="s">
-        <v>7</v>
-      </c>
-      <c r="D58" t="s">
-        <v>7</v>
-      </c>
-      <c r="E58" t="s">
+      <c r="C58" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E58" s="2" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1570,121 +1587,121 @@
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
+      <c r="A61" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B61" t="s">
+      <c r="B61" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C61" t="s">
-        <v>7</v>
-      </c>
-      <c r="D61" t="s">
-        <v>7</v>
-      </c>
-      <c r="E61" t="s">
+      <c r="C61" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E61" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
+      <c r="A62" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B62" t="s">
+      <c r="B62" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C62" t="s">
-        <v>7</v>
-      </c>
-      <c r="D62" t="s">
-        <v>7</v>
-      </c>
-      <c r="E62" t="s">
+      <c r="C62" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E62" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
+      <c r="A63" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B63" t="s">
+      <c r="B63" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C63" t="s">
-        <v>7</v>
-      </c>
-      <c r="D63" t="s">
-        <v>7</v>
-      </c>
-      <c r="E63" t="s">
+      <c r="C63" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E63" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
+      <c r="A64" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B64" t="s">
+      <c r="B64" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C64" t="s">
-        <v>7</v>
-      </c>
-      <c r="D64" t="s">
-        <v>7</v>
-      </c>
-      <c r="E64" t="s">
+      <c r="C64" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E64" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
+      <c r="A65" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B65" t="s">
+      <c r="B65" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C65" t="s">
-        <v>7</v>
-      </c>
-      <c r="D65" t="s">
-        <v>7</v>
-      </c>
-      <c r="E65" t="s">
+      <c r="C65" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E65" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
+      <c r="A66" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B66" t="s">
+      <c r="B66" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C66" t="s">
-        <v>7</v>
-      </c>
-      <c r="D66" t="s">
-        <v>7</v>
-      </c>
-      <c r="E66" t="s">
+      <c r="C66" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E66" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
+      <c r="A67" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B67" t="s">
+      <c r="B67" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C67" t="s">
-        <v>7</v>
-      </c>
-      <c r="D67" t="s">
-        <v>7</v>
-      </c>
-      <c r="E67" t="s">
+      <c r="C67" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E67" s="2" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1698,6 +1715,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E14"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="18.1796875" customWidth="1"/>
+    <col min="2" max="2" width="17.1796875" customWidth="1"/>
+    <col min="3" max="3" width="34.453125" customWidth="1"/>
+    <col min="4" max="4" width="25.1796875" customWidth="1"/>
+    <col min="5" max="5" width="34.1796875" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">

--- a/Documents/HBase/Moment冷热分离测试/Complete_STT.xlsx
+++ b/Documents/HBase/Moment冷热分离测试/Complete_STT.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Pet-Care-Ecosystem\Documents\HBase\Moment冷热分离测试\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FFFEE2A-5E3F-415F-9DD4-7F7C18036797}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD33D39D-5C59-4DBC-832E-B86325017687}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="完整状态转移表" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="52">
   <si>
     <t>当前状态</t>
   </si>
@@ -168,6 +168,18 @@
   </si>
   <si>
     <t>COLD (ARCHIVED)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>物理删除 MySQL 记录</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>物理删除 MySQL 记录，清理 HBase</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>用户删除</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -175,7 +187,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -209,6 +221,12 @@
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -247,13 +265,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -556,7 +575,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E67"/>
+  <dimension ref="A1:E56"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.36328125" customWidth="1"/>
@@ -585,7 +604,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>6</v>
@@ -601,25 +620,25 @@
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="2" t="s">
+      <c r="A3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>7</v>
+      <c r="C3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>9</v>
@@ -636,7 +655,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>10</v>
@@ -652,11 +671,11 @@
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>5</v>
+      <c r="A6" s="4" t="s">
+        <v>21</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>51</v>
       </c>
       <c r="C6" t="s">
         <v>12</v>
@@ -670,7 +689,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>5</v>
+        <v>48</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>15</v>
@@ -687,7 +706,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>16</v>
@@ -704,7 +723,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>17</v>
@@ -720,93 +739,93 @@
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B10" s="2" t="s">
+      <c r="A10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>7</v>
+      <c r="C10" t="s">
+        <v>25</v>
+      </c>
+      <c r="D10" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B11" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E11" s="2" t="s">
+      <c r="C11" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E11" s="3" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B12" s="2" t="s">
+      <c r="A12" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E12" s="2" t="s">
+      <c r="C12" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E12" s="3" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B13" s="2" t="s">
+      <c r="A13" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>7</v>
+      <c r="C13" t="s">
+        <v>28</v>
+      </c>
+      <c r="D13" t="s">
+        <v>27</v>
+      </c>
+      <c r="E13" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>21</v>
-      </c>
-      <c r="B14" t="s">
+      <c r="A14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C14" t="s">
-        <v>22</v>
-      </c>
-      <c r="D14" t="s">
-        <v>23</v>
-      </c>
-      <c r="E14" t="s">
-        <v>24</v>
+      <c r="C14" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>9</v>
@@ -823,7 +842,7 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>10</v>
@@ -839,25 +858,25 @@
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B17" s="2" t="s">
+      <c r="A17" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B17" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>7</v>
+      <c r="C17" t="s">
+        <v>12</v>
+      </c>
+      <c r="D17" t="s">
+        <v>13</v>
+      </c>
+      <c r="E17" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>15</v>
@@ -874,7 +893,7 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>16</v>
@@ -890,161 +909,161 @@
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
+      <c r="A20" t="s">
+        <v>27</v>
+      </c>
+      <c r="B20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C20" t="s">
+        <v>30</v>
+      </c>
+      <c r="D20" t="s">
         <v>21</v>
       </c>
-      <c r="B20" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>7</v>
+      <c r="E20" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>21</v>
-      </c>
-      <c r="B21" t="s">
+      <c r="A21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B21" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C21" t="s">
-        <v>25</v>
-      </c>
-      <c r="D21" t="s">
+      <c r="C21" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>27</v>
+      </c>
+      <c r="B22" t="s">
+        <v>19</v>
+      </c>
+      <c r="C22" t="s">
+        <v>32</v>
+      </c>
+      <c r="D22" t="s">
+        <v>33</v>
+      </c>
+      <c r="E22" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>27</v>
+      </c>
+      <c r="B23" t="s">
+        <v>20</v>
+      </c>
+      <c r="C23" t="s">
+        <v>35</v>
+      </c>
+      <c r="D23" t="s">
+        <v>36</v>
+      </c>
+      <c r="E23" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E21" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>27</v>
-      </c>
-      <c r="B24" t="s">
+      <c r="B24" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C24" t="s">
-        <v>28</v>
-      </c>
-      <c r="D24" t="s">
-        <v>27</v>
-      </c>
-      <c r="E24" t="s">
-        <v>29</v>
+      <c r="C24" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B25" s="2" t="s">
+      <c r="A25" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B25" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C25" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E25" s="2" t="s">
+      <c r="C25" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E25" s="3" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B26" s="2" t="s">
+      <c r="A26" t="s">
+        <v>23</v>
+      </c>
+      <c r="B26" t="s">
         <v>9</v>
       </c>
-      <c r="C26" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>7</v>
+      <c r="C26" t="s">
+        <v>38</v>
+      </c>
+      <c r="D26" t="s">
+        <v>27</v>
+      </c>
+      <c r="E26" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B27" s="2" t="s">
+      <c r="A27" t="s">
+        <v>23</v>
+      </c>
+      <c r="B27" t="s">
         <v>10</v>
       </c>
-      <c r="C27" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>7</v>
+      <c r="C27" t="s">
+        <v>40</v>
+      </c>
+      <c r="D27" t="s">
+        <v>41</v>
+      </c>
+      <c r="E27" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B28" s="2" t="s">
+      <c r="A28" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B28" t="s">
         <v>11</v>
       </c>
-      <c r="C28" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>7</v>
+      <c r="C28" t="s">
+        <v>12</v>
+      </c>
+      <c r="D28" t="s">
+        <v>13</v>
+      </c>
+      <c r="E28" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>15</v>
@@ -1061,7 +1080,7 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>16</v>
@@ -1077,195 +1096,195 @@
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>27</v>
-      </c>
-      <c r="B31" t="s">
+      <c r="A31" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B31" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C31" t="s">
-        <v>30</v>
-      </c>
-      <c r="D31" t="s">
-        <v>21</v>
-      </c>
-      <c r="E31" t="s">
-        <v>31</v>
+      <c r="C31" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B32" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B32" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C32" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E32" s="3" t="s">
+      <c r="C32" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E32" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>27</v>
-      </c>
-      <c r="B33" t="s">
+      <c r="A33" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B33" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C33" t="s">
-        <v>32</v>
-      </c>
-      <c r="D33" t="s">
-        <v>33</v>
-      </c>
-      <c r="E33" t="s">
-        <v>34</v>
+      <c r="C33" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>27</v>
-      </c>
-      <c r="B34" t="s">
+      <c r="A34" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B34" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C34" t="s">
-        <v>35</v>
-      </c>
-      <c r="D34" t="s">
-        <v>36</v>
-      </c>
-      <c r="E34" t="s">
-        <v>37</v>
+      <c r="C34" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="3" t="s">
+      <c r="A35" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B39" t="s">
+        <v>11</v>
+      </c>
+      <c r="C39" t="s">
+        <v>12</v>
+      </c>
+      <c r="D39" t="s">
+        <v>13</v>
+      </c>
+      <c r="E39" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>41</v>
+      </c>
+      <c r="B40" t="s">
+        <v>15</v>
+      </c>
+      <c r="C40" t="s">
+        <v>40</v>
+      </c>
+      <c r="D40" t="s">
+        <v>43</v>
+      </c>
+      <c r="E40" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>41</v>
+      </c>
+      <c r="B41" t="s">
+        <v>16</v>
+      </c>
+      <c r="C41" t="s">
+        <v>40</v>
+      </c>
+      <c r="D41" t="s">
         <v>23</v>
       </c>
-      <c r="B35" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E36" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>23</v>
-      </c>
-      <c r="B37" t="s">
-        <v>9</v>
-      </c>
-      <c r="C37" t="s">
-        <v>38</v>
-      </c>
-      <c r="D37" t="s">
-        <v>27</v>
-      </c>
-      <c r="E37" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>23</v>
-      </c>
-      <c r="B38" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" t="s">
-        <v>40</v>
-      </c>
-      <c r="D38" t="s">
-        <v>41</v>
-      </c>
-      <c r="E38" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>7</v>
+      <c r="E41" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>17</v>
@@ -1282,7 +1301,7 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>18</v>
@@ -1299,7 +1318,7 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>19</v>
@@ -1316,7 +1335,7 @@
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>20</v>
@@ -1333,7 +1352,7 @@
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>6</v>
@@ -1350,7 +1369,7 @@
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>8</v>
@@ -1366,93 +1385,93 @@
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" s="2" t="s">
+      <c r="A48" t="s">
+        <v>43</v>
+      </c>
+      <c r="B48" t="s">
+        <v>9</v>
+      </c>
+      <c r="C48" t="s">
+        <v>46</v>
+      </c>
+      <c r="D48" t="s">
+        <v>27</v>
+      </c>
+      <c r="E48" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>43</v>
+      </c>
+      <c r="B49" t="s">
+        <v>10</v>
+      </c>
+      <c r="C49" t="s">
+        <v>40</v>
+      </c>
+      <c r="D49" t="s">
         <v>41</v>
       </c>
-      <c r="B48" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A49" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E49" s="2" t="s">
-        <v>7</v>
+      <c r="E49" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A50" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B50" s="2" t="s">
+      <c r="A50" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B50" t="s">
         <v>11</v>
       </c>
-      <c r="C50" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>7</v>
+      <c r="C50" t="s">
+        <v>12</v>
+      </c>
+      <c r="D50" t="s">
+        <v>13</v>
+      </c>
+      <c r="E50" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>41</v>
-      </c>
-      <c r="B51" t="s">
+      <c r="A51" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B51" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C51" t="s">
-        <v>40</v>
-      </c>
-      <c r="D51" t="s">
+      <c r="C51" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="E51" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>41</v>
-      </c>
-      <c r="B52" t="s">
+      <c r="B52" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C52" t="s">
-        <v>40</v>
-      </c>
-      <c r="D52" t="s">
-        <v>23</v>
-      </c>
-      <c r="E52" t="s">
-        <v>45</v>
+      <c r="C52" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>17</v>
@@ -1469,7 +1488,7 @@
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>18</v>
@@ -1486,7 +1505,7 @@
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>19</v>
@@ -1503,7 +1522,7 @@
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>20</v>
@@ -1515,193 +1534,6 @@
         <v>7</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A57" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E57" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A58" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E58" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>43</v>
-      </c>
-      <c r="B59" t="s">
-        <v>9</v>
-      </c>
-      <c r="C59" t="s">
-        <v>46</v>
-      </c>
-      <c r="D59" t="s">
-        <v>27</v>
-      </c>
-      <c r="E59" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>43</v>
-      </c>
-      <c r="B60" t="s">
-        <v>10</v>
-      </c>
-      <c r="C60" t="s">
-        <v>40</v>
-      </c>
-      <c r="D60" t="s">
-        <v>41</v>
-      </c>
-      <c r="E60" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A61" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B61" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E61" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A62" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B62" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D62" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E62" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A63" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B63" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C63" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D63" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E63" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A64" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B64" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C64" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D64" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E64" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A65" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B65" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C65" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D65" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E65" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A66" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B66" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C66" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D66" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E66" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A67" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B67" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C67" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D67" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E67" s="2" t="s">
         <v>7</v>
       </c>
     </row>

--- a/Documents/HBase/Moment冷热分离测试/Complete_STT.xlsx
+++ b/Documents/HBase/Moment冷热分离测试/Complete_STT.xlsx
@@ -1,22 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Pet-Care-Ecosystem\Documents\HBase\Moment冷热分离测试\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Documents\GitHub\Pet-Care-Ecosystem\Documents\HBase\Moment冷热分离测试\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD33D39D-5C59-4DBC-832E-B86325017687}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220"/>
   </bookViews>
   <sheets>
     <sheet name="完整状态转移表" sheetId="1" r:id="rId1"/>
     <sheet name="原始STT（参考）" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
@@ -186,7 +185,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -275,7 +274,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -574,7 +573,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E56"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1544,7 +1543,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E14"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
